--- a/www/ig/fhir/mesures/StructureDefinition-mesures-observation-waist-circumference.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-observation-waist-circumference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -493,7 +493,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -517,7 +517,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -560,7 +560,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -643,7 +643,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -660,7 +660,7 @@
   </si>
   <si>
     <t>Motif de la mesure
-Texte libre (ex. surpoids ou obésité, diabète, maladie du cœur et des vaisseaux, tabac…)</t>
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -718,7 +718,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -747,7 +747,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -827,7 +827,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1082,7 +1082,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1165,7 +1165,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1283,7 +1283,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1493,7 +1493,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1558,7 +1558,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1614,7 +1614,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1647,7 +1647,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1659,7 +1659,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1768,7 +1768,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1818,7 +1818,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1851,7 +1851,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1888,7 +1888,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2351,17 +2351,17 @@
   <dimension ref="A1:AP96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2370,28 +2370,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5156,7 +5156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>263</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>269</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>282</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>300</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>336</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>358</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>385</v>
       </c>
@@ -8296,7 +8296,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>414</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>467</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>535</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>610</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>620</v>
       </c>
@@ -13478,7 +13478,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>626</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>635</v>
       </c>
@@ -13968,12 +13968,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP96">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
